--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -30589,16 +30589,16 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="O174" t="n">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>3.074143492938064</v>
+        <v>3.110871611133262</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -31281,16 +31281,16 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O178" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.09883646611339433</v>
+        <v>0.1007744360371864</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -33553,16 +33553,16 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="O192" t="n">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="Q192" t="n">
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>0.6280508211378841</v>
+        <v>0.7565992348210768</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -34097,16 +34097,16 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O195" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20872</v>
+        <v>20924</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -27477,16 +27477,16 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="O155" t="n">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1489024300040756</v>
+        <v>0.1755924882123533</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -30737,16 +30737,16 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>22</v>
+        <v>219</v>
       </c>
       <c r="O175" t="n">
-        <v>22</v>
+        <v>219</v>
       </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>0.01030142597512473</v>
+        <v>0.1025460131160144</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20924</v>
+        <v>21178</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -32077,16 +32077,16 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="O180" t="n">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>3.121890046591822</v>
+        <v>3.140254105689421</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -35041,16 +35041,16 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="O198" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.8704564012261903</v>
+        <v>1.021041685826502</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -35585,16 +35585,16 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O201" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -36207,6 +36207,154 @@
       <c r="BC204" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>70</v>
+      </c>
+      <c r="O205" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>0</v>
+      </c>
+      <c r="R205" t="n">
+        <v>0.05717658852960364</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36243,7 +36391,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -36326,7 +36474,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -36336,7 +36484,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -36388,7 +36536,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21226</v>
+        <v>21343</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1602,9 +1599,6 @@
       <c r="O7" t="n">
         <v>22</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -1998,9 +1992,6 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -2146,9 +2137,6 @@
       <c r="O10" t="n">
         <v>61</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1182161653513148</v>
       </c>
@@ -2294,9 +2282,6 @@
       <c r="O11" t="n">
         <v>196</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>3.467192618559192</v>
       </c>
@@ -2939,7 +2924,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3086,9 +3071,6 @@
       <c r="O15" t="n">
         <v>28</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.2616566519919337</v>
       </c>
@@ -3781,9 +3763,6 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4489,9 +4468,6 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5197,9 +5173,6 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5905,9 +5878,6 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6906,9 +6876,6 @@
       <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7447,9 +7414,6 @@
       <c r="O40" t="n">
         <v>37</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.6581593932197309</v>
       </c>
@@ -7843,9 +7807,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7991,9 +7952,6 @@
       <c r="O43" t="n">
         <v>28</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.05426315786617728</v>
       </c>
@@ -8139,9 +8097,6 @@
       <c r="O44" t="n">
         <v>163</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>2.883430596046675</v>
       </c>
@@ -8784,7 +8739,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -8931,9 +8886,6 @@
       <c r="O48" t="n">
         <v>16</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.1495180868525335</v>
       </c>
@@ -9330,9 +9282,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10038,9 +9987,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10746,9 +10692,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11454,9 +11397,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12455,9 +12395,6 @@
       <c r="O68" t="n">
         <v>6</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12996,9 +12933,6 @@
       <c r="O71" t="n">
         <v>22</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -13392,9 +13326,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -13540,9 +13471,6 @@
       <c r="O74" t="n">
         <v>27</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.05232518794238524</v>
       </c>
@@ -13688,9 +13616,6 @@
       <c r="O75" t="n">
         <v>133</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>2.352737848308023</v>
       </c>
@@ -14333,7 +14258,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14480,9 +14405,6 @@
       <c r="O79" t="n">
         <v>13</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -15027,9 +14949,6 @@
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -15735,9 +15654,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16443,9 +16359,6 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -17151,9 +17064,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17859,9 +17769,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18268,9 +18175,6 @@
       <c r="O100" t="n">
         <v>693</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>2.545258590927215</v>
       </c>
@@ -18416,9 +18320,6 @@
       <c r="O101" t="n">
         <v>416</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.194790600256904</v>
       </c>
@@ -18564,9 +18465,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19105,9 +19003,6 @@
       <c r="O105" t="n">
         <v>27</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.4802784761333171</v>
       </c>
@@ -19501,9 +19396,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19649,9 +19541,6 @@
       <c r="O108" t="n">
         <v>20</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.03875939847584092</v>
       </c>
@@ -19797,9 +19686,6 @@
       <c r="O109" t="n">
         <v>120</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>2.122770990954607</v>
       </c>
@@ -20193,9 +20079,6 @@
       <c r="O111" t="n">
         <v>110</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>2.080386513119012</v>
       </c>
@@ -20442,7 +20325,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -20589,9 +20472,6 @@
       <c r="O113" t="n">
         <v>16</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1495180868525335</v>
       </c>
@@ -20985,9 +20865,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -21432,9 +21309,6 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22140,9 +22014,6 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22848,9 +22719,6 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -23556,9 +23424,6 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23965,9 +23830,6 @@
       <c r="O132" t="n">
         <v>652</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>2.394673306326903</v>
       </c>
@@ -24113,9 +23975,6 @@
       <c r="O133" t="n">
         <v>405</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.1896398872693416</v>
       </c>
@@ -24261,9 +24120,6 @@
       <c r="O134" t="n">
         <v>9</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24802,9 +24658,6 @@
       <c r="O137" t="n">
         <v>30</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.5336427512592412</v>
       </c>
@@ -25198,9 +25051,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -25346,9 +25196,6 @@
       <c r="O140" t="n">
         <v>18</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.03488345862825683</v>
       </c>
@@ -25494,9 +25341,6 @@
       <c r="O141" t="n">
         <v>110</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>1.945873408375057</v>
       </c>
@@ -25890,9 +25734,6 @@
       <c r="O143" t="n">
         <v>194</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>3.669045304955348</v>
       </c>
@@ -26139,7 +25980,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -26286,9 +26127,6 @@
       <c r="O145" t="n">
         <v>25</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.2336220107070837</v>
       </c>
@@ -26981,9 +26819,6 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28426,9 +28261,6 @@
       <c r="O158" t="n">
         <v>43</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -28574,9 +28406,6 @@
       <c r="O159" t="n">
         <v>811</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>2.97865038563055</v>
       </c>
@@ -28722,9 +28551,6 @@
       <c r="O160" t="n">
         <v>375</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1755924882123533</v>
       </c>
@@ -29018,9 +28844,6 @@
       <c r="O162" t="n">
         <v>31</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.5514308429678827</v>
       </c>
@@ -29414,9 +29237,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -29562,9 +29382,6 @@
       <c r="O165" t="n">
         <v>30</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.05813909771376138</v>
       </c>
@@ -29710,9 +29527,6 @@
       <c r="O166" t="n">
         <v>143</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>2.529635430887574</v>
       </c>
@@ -30106,9 +29920,6 @@
       <c r="O168" t="n">
         <v>164</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>3.101667165013799</v>
       </c>
@@ -30355,7 +30166,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -30502,9 +30313,6 @@
       <c r="O170" t="n">
         <v>22</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.2055873694222336</v>
       </c>
@@ -30898,9 +30706,6 @@
       <c r="O172" t="n">
         <v>93</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.07596318190361626</v>
       </c>
@@ -31046,9 +30851,6 @@
       <c r="O173" t="n">
         <v>76</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.02177428980904733</v>
       </c>
@@ -31194,9 +30996,6 @@
       <c r="O174" t="n">
         <v>99</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.08086403234901086</v>
       </c>
@@ -31342,9 +31141,6 @@
       <c r="O175" t="n">
         <v>63</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01804974023644713</v>
       </c>
@@ -31490,9 +31286,6 @@
       <c r="O176" t="n">
         <v>80</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.06534467260526131</v>
       </c>
@@ -31638,9 +31431,6 @@
       <c r="O177" t="n">
         <v>64</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.01833624404972407</v>
       </c>
@@ -31786,9 +31576,6 @@
       <c r="O178" t="n">
         <v>85</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.06942871464309014</v>
       </c>
@@ -31934,9 +31721,6 @@
       <c r="O179" t="n">
         <v>79</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.02263380124887814</v>
       </c>
@@ -32082,9 +31866,6 @@
       <c r="O180" t="n">
         <v>855</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>3.140254105689421</v>
       </c>
@@ -32230,9 +32011,6 @@
       <c r="O181" t="n">
         <v>219</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.1025460131160144</v>
       </c>
@@ -32378,9 +32156,6 @@
       <c r="O182" t="n">
         <v>37</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.6581593932197309</v>
       </c>
@@ -32774,9 +32549,6 @@
       <c r="O184" t="n">
         <v>52</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.1007744360371864</v>
       </c>
@@ -32922,9 +32694,6 @@
       <c r="O185" t="n">
         <v>128</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>2.264289057018248</v>
       </c>
@@ -33318,9 +33087,6 @@
       <c r="O187" t="n">
         <v>23</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -33714,9 +33480,6 @@
       <c r="O189" t="n">
         <v>66</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.05390935489934058</v>
       </c>
@@ -33862,9 +33625,6 @@
       <c r="O190" t="n">
         <v>65</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.018622747863001</v>
       </c>
@@ -34010,9 +33770,6 @@
       <c r="O191" t="n">
         <v>90</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.07351275668091896</v>
       </c>
@@ -34158,9 +33915,6 @@
       <c r="O192" t="n">
         <v>77</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.02206079362232427</v>
       </c>
@@ -34306,9 +34060,6 @@
       <c r="O193" t="n">
         <v>80</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.06534467260526131</v>
       </c>
@@ -34454,9 +34205,6 @@
       <c r="O194" t="n">
         <v>78</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.02234729743560121</v>
       </c>
@@ -34602,9 +34350,6 @@
       <c r="O195" t="n">
         <v>62</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.05064212126907751</v>
       </c>
@@ -34750,9 +34495,6 @@
       <c r="O196" t="n">
         <v>89</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.02549883938164753</v>
       </c>
@@ -34898,9 +34640,6 @@
       <c r="O197" t="n">
         <v>62</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.05064212126907751</v>
       </c>
@@ -35046,9 +34785,6 @@
       <c r="O198" t="n">
         <v>278</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>1.021041685826502</v>
       </c>
@@ -35189,16 +34925,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O199" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R199" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -35351,10 +35084,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O200" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -35590,9 +35323,6 @@
       <c r="O201" t="n">
         <v>15</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.02906954885688069</v>
       </c>
@@ -35733,16 +35463,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="O202" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R202" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.7429698468341126</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -35895,10 +35622,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="O203" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -36134,9 +35861,6 @@
       <c r="O204" t="n">
         <v>74</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.02120128218249345</v>
       </c>
@@ -36282,9 +36006,6 @@
       <c r="O205" t="n">
         <v>70</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.05717658852960364</v>
       </c>
@@ -36355,6 +36076,151 @@
       <c r="BC205" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>67</v>
+      </c>
+      <c r="O206" t="n">
+        <v>67</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.01919575548955488</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36391,7 +36257,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -36474,7 +36340,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -36484,7 +36350,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -36536,7 +36402,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21343</v>
+        <v>21443</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -34925,13 +34925,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O199" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R199" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -35084,10 +35084,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O200" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21443</v>
+        <v>21446</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -28401,13 +28401,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O159" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="R159" t="n">
-        <v>2.97865038563055</v>
+        <v>2.98232319745007</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -34780,13 +34780,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>278</v>
+        <v>392</v>
       </c>
       <c r="O198" t="n">
-        <v>278</v>
+        <v>392</v>
       </c>
       <c r="R198" t="n">
-        <v>1.021041685826502</v>
+        <v>1.439742233251758</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21446</v>
+        <v>21561</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -24115,10 +24115,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -24271,10 +24271,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -28652,12 +28652,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28691,84 +28691,92 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>639</v>
+        <v>15</v>
       </c>
       <c r="O161" t="n">
-        <v>639</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.0452256796928386</v>
+        <v>15</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28795,17 +28803,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28839,22 +28847,39 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="O162" t="n">
-        <v>31</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.5514308429678827</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_CA_ON_PHO_IDTO_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Pertussis (Whooping Cough)</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -28862,6 +28887,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary pertussis notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28874,12 +28957,12 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_CA_ON_PHO_IDTO_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -28887,47 +28970,47 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28954,17 +29037,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28998,170 +29081,84 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>31</v>
+        <v>639</v>
       </c>
       <c r="O163" t="n">
-        <v>31</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
+        <v>639</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.0452256796928386</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -29193,12 +29190,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -29232,81 +29229,95 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>0.5514308429678827</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29333,17 +29344,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -29377,81 +29388,170 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O165" t="n">
-        <v>30</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0.05813909771376138</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29483,12 +29583,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -29522,95 +29622,81 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>2.529635430887574</v>
+        <v>0</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29637,17 +29723,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29681,170 +29767,81 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="O167" t="n">
-        <v>143</v>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE167" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF167" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN167" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.05813909771376138</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29876,12 +29873,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -29915,13 +29912,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="O168" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="R168" t="n">
-        <v>3.101667165013799</v>
+        <v>2.529635430887574</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -29930,7 +29927,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -29955,7 +29952,7 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT168" t="n">
@@ -29968,42 +29965,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -30035,12 +30032,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -30074,29 +30071,29 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="O169" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Kikhoste</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -30106,7 +30103,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -30121,7 +30118,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -30156,17 +30153,17 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly pertussis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -30189,7 +30186,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -30202,42 +30199,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -30269,12 +30266,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -30308,13 +30305,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="O170" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="R170" t="n">
-        <v>0.2055873694222336</v>
+        <v>3.101667165013799</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -30323,7 +30320,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -30348,7 +30345,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -30361,42 +30358,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30428,12 +30425,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -30467,29 +30464,29 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="O171" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>Kikhosta</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
@@ -30499,7 +30496,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -30514,7 +30511,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -30549,17 +30546,17 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly pertussis notifications.</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -30582,7 +30579,7 @@
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
@@ -30595,42 +30592,42 @@
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30662,12 +30659,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -30692,7 +30689,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -30701,81 +30698,95 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="O172" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="R172" t="n">
-        <v>0.07596318190361626</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -30802,17 +30813,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -30837,7 +30848,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -30846,81 +30857,170 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="O173" t="n">
-        <v>76</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0.02177428980904733</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -30982,7 +31082,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -30991,13 +31091,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="O174" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="R174" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.07596318190361626</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -31127,7 +31227,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -31136,13 +31236,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="O175" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="R175" t="n">
-        <v>0.01804974023644713</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -31272,7 +31372,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -31281,13 +31381,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O176" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="R176" t="n">
-        <v>0.06534467260526131</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -31417,7 +31517,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -31426,13 +31526,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O177" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R177" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.01804974023644713</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -31562,7 +31662,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -31571,13 +31671,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O178" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R178" t="n">
-        <v>0.06942871464309014</v>
+        <v>0.06534467260526131</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -31707,7 +31807,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -31716,13 +31816,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="O179" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="R179" t="n">
-        <v>0.02263380124887814</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -31822,12 +31922,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -31852,22 +31952,22 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>855</v>
+        <v>85</v>
       </c>
       <c r="O180" t="n">
-        <v>855</v>
+        <v>85</v>
       </c>
       <c r="R180" t="n">
-        <v>3.140254105689421</v>
+        <v>0.06942871464309014</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -31900,42 +32000,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31967,12 +32067,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31997,22 +32097,22 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="O181" t="n">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="R181" t="n">
-        <v>0.1025460131160144</v>
+        <v>0.02263380124887814</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -32045,42 +32145,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32112,12 +32212,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -32151,95 +32251,81 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>37</v>
+        <v>859</v>
       </c>
       <c r="O182" t="n">
-        <v>37</v>
+        <v>859</v>
       </c>
       <c r="R182" t="n">
-        <v>0.6581593932197309</v>
+        <v>3.1549453529675</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32266,17 +32352,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -32310,170 +32396,81 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="O183" t="n">
-        <v>37</v>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
+        <v>219</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.1025460131160144</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -32505,12 +32502,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32544,81 +32541,95 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="O184" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="R184" t="n">
-        <v>0.1007744360371864</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32645,17 +32656,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32689,22 +32700,39 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="O185" t="n">
-        <v>128</v>
-      </c>
-      <c r="R185" t="n">
-        <v>2.264289057018248</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>37</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -32712,6 +32740,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32724,12 +32810,12 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -32737,47 +32823,47 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -32804,17 +32890,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32848,170 +32934,81 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="O186" t="n">
-        <v>128</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.1007744360371864</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33043,12 +33040,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33082,13 +33079,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="O187" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="R187" t="n">
-        <v>0.214932249850517</v>
+        <v>2.264289057018248</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -33097,7 +33094,7 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -33122,7 +33119,7 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -33135,42 +33132,42 @@
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33202,12 +33199,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -33241,29 +33238,29 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="O188" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>Kikhosta</t>
+          <t>Kikhoste</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
@@ -33288,7 +33285,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -33323,17 +33320,17 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -33356,7 +33353,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -33369,42 +33366,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33436,12 +33433,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33466,7 +33463,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -33475,81 +33472,95 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="O189" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="R189" t="n">
-        <v>0.05390935489934058</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33576,17 +33587,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33611,7 +33622,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -33620,81 +33631,170 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="O190" t="n">
-        <v>65</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0.018622747863001</v>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33756,7 +33856,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33765,13 +33865,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O191" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="R191" t="n">
-        <v>0.07351275668091896</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -33901,7 +34001,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -33910,13 +34010,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="O192" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="R192" t="n">
-        <v>0.02206079362232427</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -34046,7 +34146,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -34055,13 +34155,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O193" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R193" t="n">
-        <v>0.06534467260526131</v>
+        <v>0.07351275668091896</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -34191,7 +34291,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -34200,13 +34300,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O194" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R194" t="n">
-        <v>0.02234729743560121</v>
+        <v>0.02206079362232427</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -34336,7 +34436,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34345,13 +34445,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="O195" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="R195" t="n">
-        <v>0.05064212126907751</v>
+        <v>0.06534467260526131</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -34481,7 +34581,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -34490,13 +34590,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="O196" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="R196" t="n">
-        <v>0.02549883938164753</v>
+        <v>0.02234729743560121</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -34626,7 +34726,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34741,12 +34841,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34771,22 +34871,22 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>392</v>
+        <v>89</v>
       </c>
       <c r="O198" t="n">
-        <v>392</v>
+        <v>89</v>
       </c>
       <c r="R198" t="n">
-        <v>1.439742233251758</v>
+        <v>0.02549883938164753</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -34819,42 +34919,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34886,12 +34986,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -34916,104 +35016,90 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="O199" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="R199" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35040,17 +35126,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35084,170 +35170,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>22</v>
+        <v>453</v>
       </c>
       <c r="O200" t="n">
-        <v>22</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
+        <v>453</v>
+      </c>
+      <c r="R200" t="n">
+        <v>1.663783754242465</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AT200" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV200" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35279,12 +35276,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35318,81 +35315,95 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="O201" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R201" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35419,17 +35430,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35463,22 +35474,39 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="O202" t="n">
-        <v>42</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.7429698468341126</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -35486,6 +35514,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35498,12 +35584,12 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -35511,47 +35597,47 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35578,17 +35664,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35622,170 +35708,81 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="O203" t="n">
-        <v>42</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.02906954885688069</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35817,12 +35814,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -35856,81 +35853,95 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O204" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="R204" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.7429698468341126</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -35957,17 +35968,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -35992,7 +36003,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36001,81 +36012,170 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="O205" t="n">
-        <v>70</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.05717658852960364</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36137,7 +36237,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -36146,13 +36246,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="O206" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R206" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -36219,6 +36319,296 @@
         </is>
       </c>
       <c r="BC206" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>70</v>
+      </c>
+      <c r="O207" t="n">
+        <v>70</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.05717658852960364</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>67</v>
+      </c>
+      <c r="O208" t="n">
+        <v>67</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.01919575548955488</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -36340,7 +36730,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -36350,7 +36740,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -36370,7 +36760,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -36402,7 +36792,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21561</v>
+        <v>21642</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -32251,13 +32251,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="O182" t="n">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="R182" t="n">
-        <v>3.1549453529675</v>
+        <v>3.169636600245579</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -35170,13 +35170,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>453</v>
+        <v>497</v>
       </c>
       <c r="O200" t="n">
-        <v>453</v>
+        <v>497</v>
       </c>
       <c r="R200" t="n">
-        <v>1.663783754242465</v>
+        <v>1.825387474301336</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -35315,13 +35315,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O201" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R201" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35474,10 +35474,10 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O202" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
@@ -35708,13 +35708,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O203" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R203" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -36611,6 +36611,151 @@
       <c r="BC208" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>76</v>
+      </c>
+      <c r="O209" t="n">
+        <v>76</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.06207743897499823</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36647,7 +36792,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -36730,7 +36875,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -36740,7 +36885,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -36792,7 +36937,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21642</v>
+        <v>21771</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -32502,12 +32502,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -32541,95 +32541,84 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>37</v>
+        <v>616</v>
       </c>
       <c r="O184" t="n">
-        <v>37</v>
+        <v>616</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.04359783832674268</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -32656,7 +32645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -32705,98 +32694,23 @@
       <c r="O185" t="n">
         <v>37</v>
       </c>
+      <c r="R185" t="n">
+        <v>0.6581593932197309</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -32890,17 +32804,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -32934,81 +32848,170 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="O186" t="n">
-        <v>52</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0.1007744360371864</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33040,12 +33043,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -33079,95 +33082,81 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="O187" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="R187" t="n">
-        <v>2.264289057018248</v>
+        <v>0.1007744360371864</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33194,7 +33183,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -33243,98 +33232,23 @@
       <c r="O188" t="n">
         <v>128</v>
       </c>
+      <c r="R188" t="n">
+        <v>2.264289057018248</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -33428,17 +33342,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33472,22 +33386,39 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="O189" t="n">
-        <v>23</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0.214932249850517</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>128</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -33495,6 +33426,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33512,7 +33501,7 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -33525,42 +33514,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33587,7 +33576,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -33636,98 +33625,23 @@
       <c r="O190" t="n">
         <v>23</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.214932249850517</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
         </is>
       </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Kikhosta</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -33821,17 +33735,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33856,7 +33770,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -33865,81 +33779,170 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="O191" t="n">
-        <v>66</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0.05390935489934058</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33971,12 +33974,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34010,13 +34013,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O192" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R192" t="n">
-        <v>0.018622747863001</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -34049,42 +34052,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34116,12 +34119,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34146,7 +34149,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -34155,13 +34158,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="O193" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="R193" t="n">
-        <v>0.07351275668091896</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -34194,42 +34197,42 @@
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34261,12 +34264,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -34300,13 +34303,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O194" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="R194" t="n">
-        <v>0.02206079362232427</v>
+        <v>0.07351275668091896</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -34339,42 +34342,42 @@
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34406,12 +34409,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34436,7 +34439,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34445,13 +34448,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O195" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R195" t="n">
-        <v>0.06534467260526131</v>
+        <v>0.02206079362232427</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -34484,42 +34487,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34551,12 +34554,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34590,13 +34593,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O196" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R196" t="n">
-        <v>0.02234729743560121</v>
+        <v>0.06534467260526131</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -34629,42 +34632,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34696,12 +34699,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34726,7 +34729,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34735,13 +34738,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="O197" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="R197" t="n">
-        <v>0.05064212126907751</v>
+        <v>0.02234729743560121</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -34774,42 +34777,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34841,12 +34844,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34880,13 +34883,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="O198" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="R198" t="n">
-        <v>0.02549883938164753</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -34919,42 +34922,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34986,12 +34989,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35016,7 +35019,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35025,13 +35028,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="O199" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="R199" t="n">
-        <v>0.05064212126907751</v>
+        <v>0.02549883938164753</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -35064,42 +35067,42 @@
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35131,12 +35134,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35161,22 +35164,22 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>497</v>
+        <v>62</v>
       </c>
       <c r="O200" t="n">
-        <v>497</v>
+        <v>62</v>
       </c>
       <c r="R200" t="n">
-        <v>1.825387474301336</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -35209,42 +35212,42 @@
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35276,12 +35279,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35315,95 +35318,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>25</v>
+        <v>497</v>
       </c>
       <c r="O201" t="n">
-        <v>25</v>
+        <v>497</v>
       </c>
       <c r="R201" t="n">
-        <v>0.4447022927160344</v>
+        <v>1.825387474301336</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35419,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35479,98 +35468,23 @@
       <c r="O202" t="n">
         <v>25</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -35664,17 +35578,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35708,81 +35622,170 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O203" t="n">
-        <v>17</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.03294548870446478</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35814,12 +35817,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -35853,95 +35856,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="O204" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="R204" t="n">
-        <v>0.7429698468341126</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35968,7 +35957,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36017,98 +36006,23 @@
       <c r="O205" t="n">
         <v>42</v>
       </c>
+      <c r="R205" t="n">
+        <v>0.7429698468341126</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36202,17 +36116,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36246,81 +36160,170 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="O206" t="n">
-        <v>74</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.02120128218249345</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36352,12 +36355,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36382,7 +36385,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36391,13 +36394,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O207" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R207" t="n">
-        <v>0.05717658852960364</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -36430,42 +36433,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36497,12 +36500,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36527,7 +36530,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36536,13 +36539,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O208" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="R208" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.05717658852960364</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -36575,42 +36578,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36642,12 +36645,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36672,7 +36675,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -36681,13 +36684,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O209" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="R209" t="n">
-        <v>0.06207743897499823</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -36720,40 +36723,185 @@
       </c>
       <c r="AV209" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>76</v>
+      </c>
+      <c r="O210" t="n">
+        <v>76</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.06207743897499823</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW209" t="inlineStr">
+      <c r="AW210" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX209" t="inlineStr">
+      <c r="AX210" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY209" t="inlineStr">
+      <c r="AY210" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ209" t="inlineStr">
+      <c r="AZ210" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA209" t="inlineStr">
+      <c r="BA210" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB209" t="inlineStr">
+      <c r="BB210" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC209" t="inlineStr">
+      <c r="BC210" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -36875,7 +37023,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -36885,7 +37033,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -36937,7 +37085,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21771</v>
+        <v>22387</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -28401,13 +28401,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="O159" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="R159" t="n">
-        <v>2.98232319745007</v>
+        <v>2.985996009269589</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -32251,13 +32251,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O182" t="n">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="R182" t="n">
-        <v>3.169636600245579</v>
+        <v>3.176982223884618</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -35318,13 +35318,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>497</v>
+        <v>603</v>
       </c>
       <c r="O201" t="n">
-        <v>497</v>
+        <v>603</v>
       </c>
       <c r="R201" t="n">
-        <v>1.825387474301336</v>
+        <v>2.214705527170433</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35463,13 +35463,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O202" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R202" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.4624903844246757</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -35622,10 +35622,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O203" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -36001,13 +36001,13 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="O205" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="R205" t="n">
-        <v>0.7429698468341126</v>
+        <v>1.238283078056854</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -36160,10 +36160,10 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="O206" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
@@ -36904,6 +36904,151 @@
       <c r="BC210" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>65</v>
+      </c>
+      <c r="O211" t="n">
+        <v>65</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.018622747863001</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36940,7 +37085,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -37023,7 +37168,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -37033,7 +37178,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -37085,7 +37230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22387</v>
+        <v>22590</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -32251,13 +32251,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="O182" t="n">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="R182" t="n">
-        <v>3.176982223884618</v>
+        <v>3.184327847523658</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -35318,13 +35318,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>603</v>
+        <v>646</v>
       </c>
       <c r="O201" t="n">
-        <v>603</v>
+        <v>646</v>
       </c>
       <c r="R201" t="n">
-        <v>2.214705527170433</v>
+        <v>2.372636435409784</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35463,13 +35463,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O202" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R202" t="n">
-        <v>0.4624903844246757</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -35622,10 +35622,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O203" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22590</v>
+        <v>22638</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -35318,13 +35318,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="O201" t="n">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="R201" t="n">
-        <v>2.372636435409784</v>
+        <v>2.45343829543922</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35463,13 +35463,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O202" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R202" t="n">
-        <v>0.5158546595505998</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -35622,10 +35622,10 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O203" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22638</v>
+        <v>22663</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -35318,13 +35318,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="O201" t="n">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="R201" t="n">
-        <v>2.45343829543922</v>
+        <v>2.493839225453937</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22663</v>
+        <v>22674</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -35318,13 +35318,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="O201" t="n">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="R201" t="n">
-        <v>2.493839225453937</v>
+        <v>2.648097321873768</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22674</v>
+        <v>22716</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -29912,13 +29912,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O168" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R168" t="n">
-        <v>2.529635430887574</v>
+        <v>2.511945672629619</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30071,10 +30071,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O169" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -32251,13 +32251,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="O182" t="n">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="R182" t="n">
-        <v>3.184327847523658</v>
+        <v>3.202691906621257</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -33581,12 +33581,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33620,13 +33620,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="O190" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="R190" t="n">
-        <v>0.214932249850517</v>
+        <v>2.98819153702549</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -33660,7 +33660,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -33673,42 +33673,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33740,12 +33740,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33779,29 +33779,29 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="O191" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Kikhosta</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -33811,7 +33811,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -33861,17 +33861,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly pertussis notifications.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -33907,42 +33907,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33974,12 +33974,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34004,7 +34004,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -34013,81 +34013,95 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="O192" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="R192" t="n">
-        <v>0.05390935489934058</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34114,17 +34128,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34149,7 +34163,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -34158,81 +34172,170 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="O193" t="n">
-        <v>65</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.018622747863001</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34294,7 +34397,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -34303,13 +34406,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="O194" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="R194" t="n">
-        <v>0.07351275668091896</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -34439,7 +34542,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34448,13 +34551,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="O195" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="R195" t="n">
-        <v>0.02206079362232427</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -34584,7 +34687,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -34593,13 +34696,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O196" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R196" t="n">
-        <v>0.06534467260526131</v>
+        <v>0.07351275668091896</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -34729,7 +34832,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34738,13 +34841,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O197" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R197" t="n">
-        <v>0.02234729743560121</v>
+        <v>0.02206079362232427</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -34874,7 +34977,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -34883,13 +34986,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="O198" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="R198" t="n">
-        <v>0.05064212126907751</v>
+        <v>0.06534467260526131</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -35019,7 +35122,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35028,13 +35131,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="O199" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="R199" t="n">
-        <v>0.02549883938164753</v>
+        <v>0.02234729743560121</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -35164,7 +35267,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -35279,12 +35382,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35309,22 +35412,22 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N201" t="n">
-        <v>721</v>
+        <v>89</v>
       </c>
       <c r="O201" t="n">
-        <v>721</v>
+        <v>89</v>
       </c>
       <c r="R201" t="n">
-        <v>2.648097321873768</v>
+        <v>0.02549883938164753</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -35357,42 +35460,42 @@
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35424,12 +35527,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35454,104 +35557,90 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N202" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="O202" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="R202" t="n">
-        <v>0.569218934676524</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35578,17 +35667,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35622,170 +35711,81 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>32</v>
+        <v>803</v>
       </c>
       <c r="O203" t="n">
-        <v>32</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
+        <v>803</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.949267891074391</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AT203" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV203" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35817,12 +35817,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -35856,81 +35856,95 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O204" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="R204" t="n">
-        <v>0.03294548870446478</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35957,17 +35971,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36001,22 +36015,39 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="O205" t="n">
-        <v>70</v>
-      </c>
-      <c r="R205" t="n">
-        <v>1.238283078056854</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>41</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -36024,6 +36055,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36036,12 +36125,12 @@
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -36049,47 +36138,47 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36116,17 +36205,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36160,170 +36249,81 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="O206" t="n">
-        <v>70</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.05813909771376138</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36355,12 +36355,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36394,81 +36394,95 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="O207" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="R207" t="n">
-        <v>0.02120128218249345</v>
+        <v>1.822045100569371</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36495,17 +36509,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36530,7 +36544,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36539,81 +36553,170 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="O208" t="n">
-        <v>70</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0.05717658852960364</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36675,7 +36778,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -36684,13 +36787,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="O209" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="R209" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -36820,7 +36923,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -36829,13 +36932,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O210" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="R210" t="n">
-        <v>0.06207743897499823</v>
+        <v>0.05717658852960364</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -36965,7 +37068,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -36974,13 +37077,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O211" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R211" t="n">
-        <v>0.018622747863001</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -37049,6 +37152,441 @@
       <c r="BC211" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>76</v>
+      </c>
+      <c r="O212" t="n">
+        <v>76</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.06207743897499823</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>65</v>
+      </c>
+      <c r="O213" t="n">
+        <v>65</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.018622747863001</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>28</v>
+      </c>
+      <c r="O214" t="n">
+        <v>28</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.02287063541184146</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37085,7 +37623,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -37168,7 +37706,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -37178,7 +37716,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -37198,7 +37736,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -37230,7 +37768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22716</v>
+        <v>23043</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -32251,13 +32251,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>872</v>
+        <v>758</v>
       </c>
       <c r="O182" t="n">
-        <v>872</v>
+        <v>758</v>
       </c>
       <c r="R182" t="n">
-        <v>3.202691906621257</v>
+        <v>2.783991359196001</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -35711,13 +35711,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>803</v>
+        <v>849</v>
       </c>
       <c r="O203" t="n">
-        <v>803</v>
+        <v>849</v>
       </c>
       <c r="R203" t="n">
-        <v>2.949267891074391</v>
+        <v>3.118217234772302</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -36249,13 +36249,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O206" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R206" t="n">
-        <v>0.05813909771376138</v>
+        <v>0.06395300748513752</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23043</v>
+        <v>22978</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -42495,13 +42495,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>758</v>
+        <v>876</v>
       </c>
       <c r="O234" t="n">
-        <v>758</v>
+        <v>876</v>
       </c>
       <c r="R234" t="n">
-        <v>2.783991359196001</v>
+        <v>3.217383153899336</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -43287,12 +43287,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -43326,13 +43326,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>0.1007744360371864</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -43365,42 +43365,42 @@
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43432,12 +43432,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -43471,95 +43471,81 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="O240" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="R240" t="n">
-        <v>2.264289057018248</v>
+        <v>0.1007744360371864</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43586,7 +43572,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -43635,98 +43621,23 @@
       <c r="O241" t="n">
         <v>128</v>
       </c>
+      <c r="R241" t="n">
+        <v>2.264289057018248</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
@@ -43820,17 +43731,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43864,22 +43775,39 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="O242" t="n">
-        <v>158</v>
-      </c>
-      <c r="R242" t="n">
-        <v>2.98819153702549</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>128</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -43887,6 +43815,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43904,7 +43890,7 @@
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -43917,42 +43903,42 @@
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43979,7 +43965,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -44028,98 +44014,23 @@
       <c r="O243" t="n">
         <v>158</v>
       </c>
+      <c r="R243" t="n">
+        <v>2.98819153702549</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U243" t="inlineStr">
         <is>
           <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly pertussis notifications.</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN243" t="b">
-        <v>1</v>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
@@ -44213,17 +44124,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -44257,22 +44168,39 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="O244" t="n">
-        <v>23</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0.214932249850517</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>158</v>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -44280,6 +44208,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly pertussis notifications.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44297,7 +44283,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -44310,42 +44296,42 @@
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44372,7 +44358,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -44421,98 +44407,23 @@
       <c r="O245" t="n">
         <v>23</v>
       </c>
+      <c r="R245" t="n">
+        <v>0.214932249850517</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U245" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Kikhosta</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
@@ -44606,17 +44517,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -44641,7 +44552,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -44650,81 +44561,170 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="O246" t="n">
-        <v>66</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.05390935489934058</v>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN246" t="b">
+        <v>1</v>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44756,12 +44756,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44795,13 +44795,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O247" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R247" t="n">
-        <v>0.018622747863001</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -44834,42 +44834,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44901,12 +44901,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44931,7 +44931,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -44940,93 +44940,81 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="O248" t="n">
-        <v>5</v>
-      </c>
-      <c r="P248" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="R248" t="n">
-        <v>0.08466328775485238</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45053,7 +45041,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -45105,98 +45093,18 @@
       <c r="P249" t="n">
         <v>5</v>
       </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R249" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN249" t="b">
-        <v>1</v>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
@@ -45290,17 +45198,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -45325,7 +45233,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -45334,81 +45242,173 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="O250" t="n">
-        <v>90</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.07351275668091896</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P250" t="n">
+        <v>5</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45440,12 +45440,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -45479,13 +45479,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O251" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="R251" t="n">
-        <v>0.02206079362232427</v>
+        <v>0.07351275668091896</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -45518,42 +45518,42 @@
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45585,12 +45585,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -45615,7 +45615,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45624,93 +45624,81 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="O252" t="n">
-        <v>2</v>
-      </c>
-      <c r="P252" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="R252" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02206079362232427</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ252" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45737,7 +45725,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -45789,98 +45777,18 @@
       <c r="P253" t="n">
         <v>2</v>
       </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R253" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -45974,17 +45882,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -46009,7 +45917,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -46018,81 +45926,173 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="O254" t="n">
-        <v>80</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.06534467260526131</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P254" t="n">
+        <v>2</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46124,12 +46124,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -46163,13 +46163,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O255" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R255" t="n">
-        <v>0.02234729743560121</v>
+        <v>0.06534467260526131</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -46202,42 +46202,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46269,12 +46269,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -46308,93 +46308,81 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="O256" t="n">
-        <v>5</v>
-      </c>
-      <c r="P256" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="R256" t="n">
-        <v>0.08466328775485238</v>
+        <v>0.02234729743560121</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46421,7 +46409,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -46473,98 +46461,18 @@
       <c r="P257" t="n">
         <v>5</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R257" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>1</v>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
@@ -46658,17 +46566,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -46693,7 +46601,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -46702,81 +46610,173 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="O258" t="n">
-        <v>62</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.05064212126907751</v>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P258" t="n">
+        <v>5</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN258" t="b">
+        <v>1</v>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46808,12 +46808,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -46847,13 +46847,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="O259" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="R259" t="n">
-        <v>0.02549883938164753</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -46886,42 +46886,42 @@
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46953,12 +46953,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -46983,7 +46983,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -46992,13 +46992,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="O260" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="R260" t="n">
-        <v>0.05064212126907751</v>
+        <v>0.02549883938164753</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -47031,42 +47031,42 @@
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47098,12 +47098,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -47137,93 +47137,81 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="O261" t="n">
-        <v>3</v>
-      </c>
-      <c r="P261" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="R261" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.05064212126907751</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47250,7 +47238,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -47302,98 +47290,18 @@
       <c r="P262" t="n">
         <v>3</v>
       </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R262" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
@@ -47487,17 +47395,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -47522,90 +47430,182 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N263" t="n">
-        <v>849</v>
+        <v>3</v>
       </c>
       <c r="O263" t="n">
-        <v>849</v>
-      </c>
-      <c r="R263" t="n">
-        <v>3.118217234772302</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P263" t="n">
+        <v>3</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47637,12 +47637,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -47676,95 +47676,81 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>46</v>
+        <v>891</v>
       </c>
       <c r="O264" t="n">
-        <v>46</v>
+        <v>891</v>
       </c>
       <c r="R264" t="n">
-        <v>0.8182522185975032</v>
+        <v>3.272475331192133</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47791,7 +47777,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -47840,98 +47826,23 @@
       <c r="O265" t="n">
         <v>46</v>
       </c>
+      <c r="R265" t="n">
+        <v>0.8182522185975032</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U265" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
@@ -48025,17 +47936,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -48069,81 +47980,170 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O266" t="n">
-        <v>33</v>
-      </c>
-      <c r="R266" t="n">
-        <v>0.06395300748513752</v>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN266" t="b">
+        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48175,12 +48175,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -48214,95 +48214,81 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="O267" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="R267" t="n">
-        <v>1.822045100569371</v>
+        <v>0.07751879695168185</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48329,7 +48315,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -48378,98 +48364,23 @@
       <c r="O268" t="n">
         <v>103</v>
       </c>
+      <c r="R268" t="n">
+        <v>1.822045100569371</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U268" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
@@ -48563,17 +48474,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -48607,81 +48518,170 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="O269" t="n">
-        <v>74</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.02120128218249345</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48713,12 +48713,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -48743,7 +48743,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -48752,13 +48752,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O270" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R270" t="n">
-        <v>0.05717658852960364</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -48791,42 +48791,42 @@
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48858,12 +48858,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -48897,93 +48897,81 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O271" t="n">
-        <v>2</v>
-      </c>
-      <c r="P271" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="R271" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05717658852960364</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49010,7 +48998,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -49062,98 +49050,18 @@
       <c r="P272" t="n">
         <v>2</v>
       </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R272" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -49247,17 +49155,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -49282,7 +49190,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -49291,81 +49199,173 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O273" t="n">
-        <v>67</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P273" t="n">
+        <v>2</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49397,12 +49397,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O274" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="R274" t="n">
-        <v>0.06207743897499823</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -49475,42 +49475,42 @@
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49542,12 +49542,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -49581,93 +49581,81 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O275" t="n">
-        <v>2</v>
-      </c>
-      <c r="P275" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="R275" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.06207743897499823</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49694,7 +49682,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -49746,98 +49734,18 @@
       <c r="P276" t="n">
         <v>2</v>
       </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R276" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -49931,17 +49839,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -49966,7 +49874,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -49975,81 +49883,173 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>65</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.018622747863001</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P277" t="n">
+        <v>2</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50081,12 +50081,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -50111,7 +50111,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -50120,13 +50120,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="O278" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="R278" t="n">
-        <v>0.02287063541184146</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -50159,42 +50159,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -50226,12 +50226,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -50265,93 +50265,81 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O279" t="n">
-        <v>3</v>
-      </c>
-      <c r="P279" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="R279" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA279" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50378,7 +50366,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -50430,98 +50418,18 @@
       <c r="P280" t="n">
         <v>3</v>
       </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R280" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN280" t="b">
-        <v>1</v>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
@@ -50615,123 +50523,360 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>3</v>
+      </c>
+      <c r="O281" t="n">
+        <v>3</v>
+      </c>
+      <c r="P281" t="n">
+        <v>3</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
+      <c r="G282" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>D028</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
         <is>
           <t>百日咳</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="K282" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="L282" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N281" t="n">
+      <c r="N282" t="n">
         <v>80</v>
       </c>
-      <c r="O281" t="n">
+      <c r="O282" t="n">
         <v>80</v>
       </c>
-      <c r="R281" t="n">
+      <c r="R282" t="n">
         <v>0.02292030506215508</v>
       </c>
-      <c r="S281" t="inlineStr">
+      <c r="S282" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO281" t="inlineStr">
+      <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP281" t="inlineStr">
+      <c r="AP282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR281" t="inlineStr">
+      <c r="AR282" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS281" t="inlineStr"/>
-      <c r="AT281" t="n">
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
         <v>0</v>
       </c>
-      <c r="AU281" t="inlineStr">
+      <c r="AU282" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV281" t="inlineStr">
+      <c r="AV282" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW281" t="inlineStr">
+      <c r="AW282" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX281" t="inlineStr">
+      <c r="AX282" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY281" t="inlineStr">
+      <c r="AY282" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ281" t="inlineStr">
+      <c r="AZ282" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA281" t="inlineStr">
+      <c r="BA282" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB281" t="inlineStr">
+      <c r="BB282" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC281" t="inlineStr">
+      <c r="BC282" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -50853,7 +50998,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -50863,7 +51008,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -50915,7 +51060,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23151</v>
+        <v>23319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -72731,13 +72731,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="O397" t="n">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="R397" t="n">
-        <v>3.819724292300581</v>
+        <v>3.860125222315299</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -74015,13 +74015,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O406" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R406" t="n">
-        <v>1.049497410809841</v>
+        <v>1.085073594227124</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -74179,10 +74179,10 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O407" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -77847,13 +77847,13 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="O428" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="R428" t="n">
-        <v>0.1138571664051135</v>
+        <v>0.2864793219225436</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -78395,13 +78395,13 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R431" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -79054,7 +79054,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29207</v>
+        <v>29268</v>
       </c>
     </row>
     <row r="16">
